--- a/results/job_matches_2026-08-15.xlsx
+++ b/results/job_matches_2026-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,12 +573,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Hadoop Solutions Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>talent source global</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -587,11 +587,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4deff5096edc72f7</t>
+          <t>https://www.indeed.com/viewjob?jk=1e611db79889b1d9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect-68464</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>talent source global</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a6ef929081a1</t>
+          <t>https://www.indeed.com/viewjob?jk=4deff5096edc72f7</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d634d7b84760169</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a6ef929081a1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (API Integrations)</t>
+          <t>Data Architect-68464</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4473ab579b8e449a</t>
+          <t>https://www.indeed.com/viewjob?jk=9d634d7b84760169</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Scientific Technical Engineer - PDS&amp;T CMC</t>
+          <t>Sr Engineer, SRE TechOps CICD (Remote)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097744a388fc20c6</t>
+          <t>https://www.indeed.com/viewjob?jk=02946a77bdd7bddf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Distinguished Engineer</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HarbourVest</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
+          <t>https://www.indeed.com/viewjob?jk=4473ab579b8e449a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Scientific Technical Engineer - PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
+          <t>https://www.indeed.com/viewjob?jk=097744a388fc20c6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
+          <t>https://www.indeed.com/viewjob?jk=986170411aab2db0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cloud Data Engineer</t>
+          <t>Sr. Engineer II, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AmTrust Financial</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Snowflake, Dimensional Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fa85e48bc32f2c8</t>
+          <t>https://www.indeed.com/viewjob?jk=e33354ecb78e1f09</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer, Development</t>
+          <t>Distinguished Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>HarbourVest</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Data Modeling, Kimball</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=90659c2e53e47134</t>
+          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Delaware Nation Industries</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer, Global</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
+          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>GCP Architect Grade C2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,67 +1056,67 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
+          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineering SMTS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, HBase, Spark, Scala, Kafka, Oracle, MongoDB</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3785e321087a42fb</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Delaware Nation Industries</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9351c1cfec6b9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Mid- Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
+          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer NEX</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Patterson-UTI Drilling Company LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
+          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
+          <t>https://www.indeed.com/viewjob?jk=e9351c1cfec6b9f3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Modeling &amp; AI Analytics</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
+          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Senior Site Reliability Engineer NEX</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Patterson-UTI Drilling Company LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7741c8e3ee80da0</t>
+          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Fredericksburg, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c167be2505d9bdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Data Modeling &amp; AI Analytics</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Buffalo, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42b8e0fc03dc2f65</t>
+          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Virginia Beach, VA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109ee650e4175aaf</t>
+          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Contact Center Data Engineer</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Amazon QuickSight, Power BI</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9e8163953cd5c49</t>
+          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>MQ Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>CloudSecurityweb</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
+          <t>https://www.indeed.com/viewjob?jk=523220d0e85b6be6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Software Engineer - Digital Site Development</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer - Digital Site Development</t>
+          <t>Senior Cloud Engineering Architect - Evinova</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4e06659b43811d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineering Architect - Evinova</t>
+          <t>Sr. Systems Administrator</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>CSCI Consulting</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Kafka, ETL, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4e06659b43811d</t>
+          <t>https://www.indeed.com/viewjob?jk=a990bfe6dafb32a5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MQ Architect</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CloudSecurityweb</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,42 +1606,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523220d0e85b6be6</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Systems Administrator</t>
+          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CSCI Consulting</t>
+          <t>True Zero Technologies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,94 +1651,94 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a990bfe6dafb32a5</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>West Lake Hls, TX, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>API Gateway, Azure, Blob Storage, Event Hubs, Scala, Kafka, Oracle, PostgreSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a873f8760103f3a</t>
+          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>QA Software Engineer NC Hybrid</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
+          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Outlook Amusements</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>La Crescenta, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Scala, SQL Server, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=842ce59e184f16a0</t>
+          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Fullstack Software Engineer, Information Security Team</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
+          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer, Information Security Team</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Slate Auto</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
+          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Slate Auto</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior AI Engineer I - Global Dining</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
+          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior AI Engineer I - Global Dining</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
+          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tree Top</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Selah, WA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
+          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Solution Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tree Top</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Selah, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
+          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Security Engineer</t>
+          <t>R&amp;D Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Dynanet Corporation</t>
+          <t>Broadcom</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, CI/CD, GitHub Actions, Azure DevOps, Terraform, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a6a52a055ba853</t>
+          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Chicago Blackhawks</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
+          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
+          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>R&amp;D Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,112 +2131,112 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>S3, RDS, Cloud Storage, Snowflake, NoSQL, dbt, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
+          <t>https://www.indeed.com/viewjob?jk=ae4f189101c570b8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer I, Research Informatics</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Mammoth Biosciences</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ba47b9ab3a0c3ab</t>
+          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Customer Reliability Engineer - Airflow</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Snowflake, NoSQL, dbt, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae4f189101c570b8</t>
+          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer - Airflow</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
+          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Senior Software Engineer, iCasino</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
+          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, iCasino</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
+          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>K Tech International</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Torrington, CT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Product Owner</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>K Tech International</t>
+          <t>Expion health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Torrington, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
+          <t>https://www.indeed.com/viewjob?jk=b2e5617ec292674d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Product Owner</t>
+          <t>Sr. Engineer, SDET - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Expion health</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e5617ec292674d</t>
+          <t>https://www.indeed.com/viewjob?jk=021b25e1008c44c5</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Microsoft Fabric Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CloudBees Inc</t>
+          <t>Landmark Properties, Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Athens, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Kafka, PostgreSQL, Cassandra, NoSQL, ELT, CI/CD, Jenkins</t>
+          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5a818a5a8c923cd</t>
+          <t>https://www.indeed.com/viewjob?jk=6ed1ad8a3c88baae</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Athens, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed1ad8a3c88baae</t>
+          <t>https://www.indeed.com/viewjob?jk=f5b4d249126be9c1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Landmark Properties, Inc.</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b4d249126be9c1</t>
+          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ROYAL ELECTRIC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
+          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>ROYAL ELECTRIC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
+          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
+          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
+          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer (Implementation &amp; Integration)</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Meduit</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer III</t>
+          <t>Data Engineer (Implementation &amp; Integration)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>Meduit</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer III</t>
+          <t>Data Warehouse Software Engineer III</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>Babel Street</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
+          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Cloud Platform Engineer III</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
+          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Edmond, OK, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
+          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Broken Arrow, OK, US USA</t>
+          <t>Edmond, OK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
+          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Broken Arrow, OK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
+          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Agentic AI, Automation, and Data Platforms</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ELT, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25402b211806bc05</t>
+          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Apps &amp; Behaviors</t>
+          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SmartThings</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Scala, MySQL, DynamoDB, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caea69b877e2e76a</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Level Data, Inc</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Application Developer/Programmer II</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Associated Grocers of New England, Inc.</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Pembroke, NH, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
+          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>Elm &amp; Oak Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer, Platform Infrastructure</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>SmarterDx</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
+          <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer – Architecture Team</t>
+          <t>Application Developer/Programmer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Rethink First</t>
+          <t>Associated Grocers of New England, Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Pembroke, NH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer III</t>
+          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8626322b450d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer III</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Level Data, Inc</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,15 +3636,190 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Waystar</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer – Architecture Team</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Rethink First</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Apps &amp; Behaviors</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SmartThings</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Minneapolis, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Scala, MySQL, DynamoDB, Terraform</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=caea69b877e2e76a</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer III</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f8626322b450d2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer III</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8d90a9d77defb25c</t>
         </is>

--- a/results/job_matches_2026-08-15.xlsx
+++ b/results/job_matches_2026-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Distinguished Engineer</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>HarbourVest</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,69 +906,69 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab09cd891b8a55c1</t>
+          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
+          <t>Full Stack Developer [development, QA automation, data]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
+          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
+          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GCP Architect Grade C2</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
+          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Architect Grade C2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Delaware Nation Industries</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer, Global</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Delaware Nation Industries</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
+          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Mid- Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9351c1cfec6b9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Software Engineering Intern</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Copart, Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
+          <t>https://www.indeed.com/viewjob?jk=e9351c1cfec6b9f3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer NEX</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Patterson-UTI Drilling Company LLC</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
+          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
+          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Modeling &amp; AI Analytics</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
+          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Senior Site Reliability Engineer NEX</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Patterson-UTI Drilling Company LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MQ Architect</t>
+          <t>Data Modeling &amp; AI Analytics</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CloudSecurityweb</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523220d0e85b6be6</t>
+          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer - Digital Site Development</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>Pharmacy Data Management, Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Poland, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
+          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineering Architect - Evinova</t>
+          <t>MQ Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>CloudSecurityweb</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Kafka, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4e06659b43811d</t>
+          <t>https://www.indeed.com/viewjob?jk=523220d0e85b6be6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Systems Administrator</t>
+          <t>Software Engineer - Digital Site Development</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CSCI Consulting</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a990bfe6dafb32a5</t>
+          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>Senior Cloud Engineering Architect - Evinova</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,69 +1606,69 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4e06659b43811d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
+          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>True Zero Technologies</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
+          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>QA Software Engineer NC Hybrid</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
+          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>QA Software Engineer NC Hybrid</t>
+          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>True Zero Technologies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
+          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
         </is>
       </c>
     </row>
@@ -1833,25 +1833,25 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Slate Auto</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior AI Engineer I - Global Dining</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
+          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior AI Engineer I - Global Dining</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Slate Auto</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
+          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
+          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tree Top</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Selah, WA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
+          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Tree Top</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Selah, WA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
+          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>R&amp;D Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Broadcom</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>S3, RDS, Cloud Storage, Snowflake, NoSQL, dbt, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79cc1d74cbb5d37b</t>
+          <t>https://www.indeed.com/viewjob?jk=ae4f189101c570b8</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solution Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Chicago Blackhawks</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,42 +2096,42 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Snowflake, PostgreSQL, MySQL, ELT, dbt, CI/CD, Airflow</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20621ff04e6c7e2a</t>
+          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SMTS IT Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Snowflake, NoSQL, dbt, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae4f189101c570b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Research Informatics</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mammoth Biosciences</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
+          <t>Senior Software Engineer, iCasino</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
+          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
         </is>
       </c>
     </row>
@@ -2253,17 +2253,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
+          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Medallion Architecture, Google Cloud Platform, GCP, Scala, Snowflake, SQL Server, Data Modeling, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d32cb461604b896</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Senior Software Engineer I, Research Informatics</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Mammoth Biosciences</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, iCasino</t>
+          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Data Analytics Specialist</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Colorado Public Employees' Retirement Association</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
+          <t>https://www.indeed.com/viewjob?jk=907539388cf5ea04</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Sr. Engineer, SDET - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=021b25e1008c44c5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>K Tech International</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Torrington, CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
+          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Product Owner</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Expion health</t>
+          <t>K Tech International</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Torrington, CT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2e5617ec292674d</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. Engineer, SDET - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=021b25e1008c44c5</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Landmark Properties, Inc.</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Athens, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ed1ad8a3c88baae</t>
+          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Microsoft Fabric Data Engineer</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Landmark Properties, Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Data Factory, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5b4d249126be9c1</t>
+          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>ROYAL ELECTRIC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,19 +2666,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
+          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ROYAL ELECTRIC</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
+          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Data Engineer (Implementation &amp; Integration)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Meduit</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Data Warehouse Software Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Babel Street</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
+          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer (Implementation &amp; Integration)</t>
+          <t>Cloud Platform Engineer III</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Meduit</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer III</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
+          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer III</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
+          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Edmond, OK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Broken Arrow, OK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
+          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Edmond, OK, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
+          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Broken Arrow, OK, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>Senior Software Engineer, Platform Infrastructure</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>SmarterDx</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
+          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Elm &amp; Oak Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
+          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Elm &amp; Oak Health</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform Infrastructure</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SmarterDx</t>
+          <t>Level Data, Inc</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
+          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Application Developer/Programmer II</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Associated Grocers of New England, Inc.</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pembroke, NH, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
+          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
+          <t>Senior Full Stack Engineer – Architecture Team</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>Rethink First</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Application Developer/Programmer II</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Level Data, Inc</t>
+          <t>Associated Grocers of New England, Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Pembroke, NH, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
+          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8626322b450d2c</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer – Architecture Team</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Rethink First</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,120 +3706,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Apps &amp; Behaviors</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>SmartThings</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, Kinesis, SQS, SNS, API Gateway, RDS, Scala, MySQL, DynamoDB, Terraform</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=caea69b877e2e76a</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer III</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8626322b450d2c</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer III</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8d90a9d77defb25c</t>
         </is>

--- a/results/job_matches_2026-08-15.xlsx
+++ b/results/job_matches_2026-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineering Intern</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9351c1cfec6b9f3</t>
+          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
+          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
         </is>
       </c>
     </row>
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
+          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,19 +1371,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Senior Site Reliability Engineer NEX</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Patterson-UTI Drilling Company LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
+          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer NEX</t>
+          <t>Data Modeling &amp; AI Analytics</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Patterson-UTI Drilling Company LLC</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
+          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Modeling &amp; AI Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Pharmacy Data Management, Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Poland, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
+          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MQ Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pharmacy Data Management, Inc.</t>
+          <t>CloudSecurityweb</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
+          <t>https://www.indeed.com/viewjob?jk=523220d0e85b6be6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MQ Architect</t>
+          <t>Software Engineer - Digital Site Development</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CloudSecurityweb</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523220d0e85b6be6</t>
+          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer - Digital Site Development</t>
+          <t>Senior Cloud Engineering Architect - Evinova</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4e06659b43811d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineering Architect - Evinova</t>
+          <t>QA Software Engineer NC Hybrid</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Kafka, ETL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,59 +1616,59 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4e06659b43811d</t>
+          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer (Python / Cloud / React)</t>
+          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EXL Service</t>
+          <t>True Zero Technologies</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7f78b2330159794</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QA Software Engineer NC Hybrid</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
+          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>True Zero Technologies</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
+          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Senior AI Engineer I - Global Dining</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
+          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Fullstack Software Engineer, Information Security Team</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Slate Auto</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ac61fa1a48bebaf</t>
+          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
+          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior AI Engineer I - Global Dining</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
+          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Slate Auto</t>
+          <t>Tree Top</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Selah, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>S3, RDS, Cloud Storage, Snowflake, NoSQL, dbt, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
+          <t>https://www.indeed.com/viewjob?jk=ae4f189101c570b8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solution Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
+          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>SMTS IT Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tree Top</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Selah, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
+          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Snowflake, NoSQL, dbt, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae4f189101c570b8</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>Senior Software Engineer, iCasino</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
+          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SMTS IT Engineer</t>
+          <t>Customer Reliability Engineer - Airflow</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
+          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
+          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, iCasino</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer - Airflow</t>
+          <t>Senior Software Engineer I, Research Informatics</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Mammoth Biosciences</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
+          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
+          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Research Informatics</t>
+          <t>Sr. Engineer, SDET - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mammoth Biosciences</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
+          <t>https://www.indeed.com/viewjob?jk=021b25e1008c44c5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>K Tech International</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Torrington, CT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Analytics Specialist</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Colorado Public Employees' Retirement Association</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=907539388cf5ea04</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Engineer, SDET - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=021b25e1008c44c5</t>
+          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>K Tech International</t>
+          <t>ROYAL ELECTRIC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Torrington, CT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,19 +2526,19 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
+          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ROYAL ELECTRIC</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
+          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Data Engineer (Implementation &amp; Integration)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Meduit</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Data Warehouse Software Engineer III</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Babel Street</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
+          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Cloud Platform Engineer III</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
+          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
+          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer (Implementation &amp; Integration)</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Meduit</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer III</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
+          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer III</t>
+          <t>Senior Platform/DevOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>REGENT BANK</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Edmond, OK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
+          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Broken Arrow, OK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Edmond, OK, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Broken Arrow, OK, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
+          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
+          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>Senior Software Engineer, Platform Infrastructure</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>SmarterDx</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
+          <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Elm &amp; Oak Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
+          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform Infrastructure</t>
+          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SmarterDx</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Level Data, Inc</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
+          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
+          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Full Stack Engineer – Architecture Team</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Elm &amp; Oak Health</t>
+          <t>Rethink First</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
+          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
+          <t>Application Developer/Programmer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>Associated Grocers of New England, Inc.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Pembroke, NH, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Level Data, Inc</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
+          <t>https://www.indeed.com/viewjob?jk=3f8626322b450d2c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3575,146 +3575,6 @@
         </is>
       </c>
       <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer – Architecture Team</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Rethink First</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Application Developer/Programmer II</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Associated Grocers of New England, Inc.</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Pembroke, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer III</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8626322b450d2c</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer III</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8d90a9d77defb25c</t>
         </is>

--- a/results/job_matches_2026-08-15.xlsx
+++ b/results/job_matches_2026-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,47 +573,47 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Hadoop Solutions Developer</t>
+          <t>SR Azure Data Factory- Remote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20.8</v>
+        <v>21.5</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e611db79889b1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8625d99e5c7e4a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Hadoop Solutions Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>talent source global</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4deff5096edc72f7</t>
+          <t>https://www.indeed.com/viewjob?jk=1e611db79889b1d9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Architect-68464</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>talent source global</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,102 +671,102 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a6ef929081a1</t>
+          <t>https://www.indeed.com/viewjob?jk=4deff5096edc72f7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Architect-68464</t>
+          <t>Senior Java AWS Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d634d7b84760169</t>
+          <t>https://www.indeed.com/viewjob?jk=356ce32716bcc358</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Engineer, SRE TechOps CICD (Remote)</t>
+          <t>Senior Java AWS Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02946a77bdd7bddf</t>
+          <t>https://www.indeed.com/viewjob?jk=88370938985e0439</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (API Integrations)</t>
+          <t>Data Architect-68464</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>19.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4473ab579b8e449a</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a6ef929081a1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Scientific Technical Engineer - PDS&amp;T CMC</t>
+          <t>Data Architect-68464</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>19.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,14 +811,14 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097744a388fc20c6</t>
+          <t>https://www.indeed.com/viewjob?jk=9d634d7b84760169</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Sr Engineer, SRE TechOps CICD (Remote)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,15 +828,15 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>18.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986170411aab2db0</t>
+          <t>https://www.indeed.com/viewjob?jk=02946a77bdd7bddf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Engineer II, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33354ecb78e1f09</t>
+          <t>https://www.indeed.com/viewjob?jk=4473ab579b8e449a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Technical Software Engineer</t>
+          <t>Scientific Technical Engineer - PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
+          <t>https://www.indeed.com/viewjob?jk=097744a388fc20c6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack Developer [development, QA automation, data]</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
+          <t>https://www.indeed.com/viewjob?jk=986170411aab2db0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
+          <t>Sr. Engineer II, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
+          <t>https://www.indeed.com/viewjob?jk=e33354ecb78e1f09</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
+          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Full Stack Developer [development, QA automation, data]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
+          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GCP Architect Grade C2</t>
+          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
+          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Delaware Nation Industries</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
+          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>GCP Architect Grade C2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
+          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer, Global</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Delaware Nation Industries</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
+          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
+          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer NEX</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Patterson-UTI Drilling Company LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,89 +1406,89 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
+          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Modeling &amp; AI Analytics</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Mid- Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pharmacy Data Management, Inc.</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
+          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MQ Architect</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CloudSecurityweb</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1497,11 +1497,11 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523220d0e85b6be6</t>
+          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer - Digital Site Development</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
+          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineering Architect - Evinova</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Kafka, ETL, CI/CD</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4e06659b43811d</t>
+          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QA Software Engineer NC Hybrid</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
+          <t>Senior Site Reliability Engineer NEX</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>True Zero Technologies</t>
+          <t>Patterson-UTI Drilling Company LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
+          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Data Modeling &amp; AI Analytics</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
+          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Pharmacy Data Management, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Poland, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
+          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>MQ Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>CloudSecurityweb</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
+          <t>https://www.indeed.com/viewjob?jk=523220d0e85b6be6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior AI Engineer I - Global Dining</t>
+          <t>Software Engineer - Digital Site Development</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
+          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Cloud Engineering Architect - Evinova</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Slate Auto</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4e06659b43811d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>QA Software Engineer NC Hybrid</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
+          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>True Zero Technologies</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tree Top</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Selah, WA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
+          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Snowflake, NoSQL, dbt, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae4f189101c570b8</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
+          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SMTS IT Engineer</t>
+          <t>Senior AI Engineer I - Global Dining</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
+          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Slate Auto</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
+          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, iCasino</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,67 +2106,67 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer - Airflow</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Tree Top</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Selah, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
+          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
+          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>S3, RDS, Cloud Storage, Snowflake, NoSQL, dbt, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
+          <t>https://www.indeed.com/viewjob?jk=ae4f189101c570b8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Research Informatics</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mammoth Biosciences</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
+          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
+          <t>Solution Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
+          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>SMTS IT Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Engineer, SDET - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=021b25e1008c44c5</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer, iCasino</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>K Tech International</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Torrington, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
+          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Customer Reliability Engineer - Airflow</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
+          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer I, Research Informatics</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ROYAL ELECTRIC</t>
+          <t>Mammoth Biosciences</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
+          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Agentic AI Engineering Architect (Remote -US)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
+          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
+          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
+          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>K Tech International</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Torrington, CT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Sr. Engineer, SDET - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
+          <t>https://www.indeed.com/viewjob?jk=021b25e1008c44c5</t>
         </is>
       </c>
     </row>
@@ -2806,19 +2806,19 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer (Implementation &amp; Integration)</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Meduit</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer III</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
+          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>ROYAL ELECTRIC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
+          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f91e06aebfaaaf1</t>
+          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72ef0bc51a24bc5</t>
+          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd71a8cfa1a8aaab</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Edmond, OK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6751bf17199336e8</t>
+          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Broken Arrow, OK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bac113fb34bfff49</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Platform/DevOps Engineer</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>REGENT BANK</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Blob Storage, Snowflake, Power BI, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f281c3de1a5cf3c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Data Engineer (Implementation &amp; Integration)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Meduit</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Warehouse Software Engineer III</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Babel Street</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform Infrastructure</t>
+          <t>Cloud Platform Engineer III</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SmarterDx</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
+          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Elm &amp; Oak Health</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
+          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Level Data, Inc</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
+          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Full Stack Engineer – Architecture Team</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Rethink First</t>
+          <t>Elm &amp; Oak Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Application Developer/Programmer II</t>
+          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Associated Grocers of New England, Inc.</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Pembroke, NH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer III</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Level Data, Inc</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8626322b450d2c</t>
+          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer III</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,15 +3566,190 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Engineer – Architecture Team</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Rethink First</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Application Developer/Programmer II</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Associated Grocers of New England, Inc.</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Pembroke, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Platform Infrastructure</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SmarterDx</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer III</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3f8626322b450d2c</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer III</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=8d90a9d77defb25c</t>
         </is>

--- a/results/job_matches_2026-08-15.xlsx
+++ b/results/job_matches_2026-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Apache Spark Developer</t>
+          <t>Databricks Solution Architect - Onsite- W2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.9</v>
+        <v>22.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Step Functions, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Google Cloud Platform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86da01562515eb49</t>
+          <t>https://www.indeed.com/viewjob?jk=c7af5960a321f1aa</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SR Azure Data Factory- Remote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.8</v>
+        <v>21.5</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Hadoop</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89ec0c153166e42d</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8625d99e5c7e4a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Databricks Solution Architect - Onsite- W2</t>
+          <t>Hadoop Solutions Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>22.9</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Google Cloud Platform</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,94 +566,94 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7af5960a321f1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=1e611db79889b1d9</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SR Azure Data Factory- Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>talent source global</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8625d99e5c7e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=4deff5096edc72f7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Hadoop Solutions Developer</t>
+          <t>Senior Java AWS Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e611db79889b1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=356ce32716bcc358</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java AWS Developer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>talent source global</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,112 +661,112 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4deff5096edc72f7</t>
+          <t>https://www.indeed.com/viewjob?jk=88370938985e0439</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Java AWS Developer</t>
+          <t>Data Architect-68464</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356ce32716bcc358</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a6ef929081a1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Java AWS Developer</t>
+          <t>Data Architect-68464</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88370938985e0439</t>
+          <t>https://www.indeed.com/viewjob?jk=9d634d7b84760169</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect-68464</t>
+          <t>Sr Engineer, SRE TechOps CICD (Remote)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a6ef929081a1</t>
+          <t>https://www.indeed.com/viewjob?jk=02946a77bdd7bddf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Architect-68464</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>19.4</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d634d7b84760169</t>
+          <t>https://www.indeed.com/viewjob?jk=4473ab579b8e449a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Engineer, SRE TechOps CICD (Remote)</t>
+          <t>Scientific Technical Engineer - PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02946a77bdd7bddf</t>
+          <t>https://www.indeed.com/viewjob?jk=097744a388fc20c6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (API Integrations)</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4473ab579b8e449a</t>
+          <t>https://www.indeed.com/viewjob?jk=986170411aab2db0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Scientific Technical Engineer - PDS&amp;T CMC</t>
+          <t>Sr. Engineer II, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097744a388fc20c6</t>
+          <t>https://www.indeed.com/viewjob?jk=e33354ecb78e1f09</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Full Stack Developer [development, QA automation, data]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
+          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986170411aab2db0</t>
+          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Engineer II, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33354ecb78e1f09</t>
+          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Technical Software Engineer</t>
+          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
+          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack Developer [development, QA automation, data]</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
+          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>GCP Architect Grade C2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
+          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GCP Architect Grade C2</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Delaware Nation Industries</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
+          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Delaware Nation Industries</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
+          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
         </is>
       </c>
     </row>
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
+          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
+          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1366,29 +1366,29 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Mid- Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
+          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,42 +1431,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer, Global</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
+          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
+          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Senior Site Reliability Engineer NEX</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Patterson-UTI Drilling Company LLC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Data Modeling &amp; AI Analytics</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
+          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer NEX</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Patterson-UTI Drilling Company LLC</t>
+          <t>Pharmacy Data Management, Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Poland, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
+          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Modeling &amp; AI Analytics</t>
+          <t>MQ Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>CloudSecurityweb</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
+          <t>https://www.indeed.com/viewjob?jk=523220d0e85b6be6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Digital Site Development</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pharmacy Data Management, Inc.</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
+          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MQ Architect</t>
+          <t>Senior Cloud Engineering Architect - Evinova</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CloudSecurityweb</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523220d0e85b6be6</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4e06659b43811d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer - Digital Site Development</t>
+          <t>Software Engineer II - AI/ML Developer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
+          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineering Architect - Evinova</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Kafka, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4e06659b43811d</t>
+          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
         </is>
       </c>
     </row>
@@ -2113,17 +2113,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tree Top</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Selah, WA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
+          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tree Top</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Selah, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
+          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
         </is>
       </c>
     </row>
@@ -2743,25 +2743,25 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Engineer, SDET - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=021b25e1008c44c5</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
+          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
+          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ROYAL ELECTRIC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ROYAL ELECTRIC</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
+          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
+          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
+          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Data Engineer (Implementation &amp; Integration)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Meduit</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer (Implementation &amp; Integration)</t>
+          <t>Data Warehouse Software Engineer III</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Meduit</t>
+          <t>Babel Street</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer III</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cloud Platform Engineer III</t>
+          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>University of Utah</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac880839f17e6768</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
+          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
+          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Elm &amp; Oak Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
+          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Application Developer/Programmer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Associated Grocers of New England, Inc.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Pembroke, NH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
+          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Elm &amp; Oak Health</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>Level Data, Inc</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Level Data, Inc</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
+          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer, Platform Infrastructure</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>SmarterDx</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,182 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Engineer – Architecture Team</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Rethink First</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, CI/CD, Azure DevOps, Terraform, Docker, Git</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab5430ace02a7fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Application Developer/Programmer II</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Associated Grocers of New England, Inc.</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Pembroke, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Platform Infrastructure</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>SmarterDx</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer III</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3f8626322b450d2c</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer III</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d90a9d77defb25c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-15.xlsx
+++ b/results/job_matches_2026-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -853,17 +853,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Senior Data Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
+          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986170411aab2db0</t>
+          <t>https://www.indeed.com/viewjob?jk=d460a6aac4fd260a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Engineer II, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
+          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33354ecb78e1f09</t>
+          <t>https://www.indeed.com/viewjob?jk=afe1d38414cdf113</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack Developer [development, QA automation, data]</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
+          <t>https://www.indeed.com/viewjob?jk=986170411aab2db0</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Technical Software Engineer</t>
+          <t>Sr. Engineer II, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
+          <t>https://www.indeed.com/viewjob?jk=e33354ecb78e1f09</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
+          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Full Stack Developer [development, QA automation, data]</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
+          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
+          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GCP Architect Grade C2</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>GCP Architect Grade C2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Delaware Nation Industries</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
+          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Delaware Nation Industries</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
+          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
         </is>
       </c>
     </row>
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
+          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1366,29 +1366,29 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer, Global</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
+          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,42 +1431,42 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Mid- Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
+          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
+          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer NEX</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Patterson-UTI Drilling Company LLC</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
+          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Modeling &amp; AI Analytics</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer NEX</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pharmacy Data Management, Inc.</t>
+          <t>Patterson-UTI Drilling Company LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
+          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MQ Architect</t>
+          <t>Data Modeling &amp; AI Analytics</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CloudSecurityweb</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523220d0e85b6be6</t>
+          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer - Digital Site Development</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>Pharmacy Data Management, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Poland, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
+          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineering Architect - Evinova</t>
+          <t>MQ Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>CloudSecurityweb</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Kafka, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4e06659b43811d</t>
+          <t>https://www.indeed.com/viewjob?jk=523220d0e85b6be6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML Developer</t>
+          <t>Software Engineer - Digital Site Development</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
+          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Senior Cloud Engineering Architect - Evinova</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4e06659b43811d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>QA Software Engineer NC Hybrid</t>
+          <t>Software Engineer II - AI/ML Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
+          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>True Zero Technologies</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
+          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>QA Software Engineer NC Hybrid</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
+          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>True Zero Technologies</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AI Engineer I - Global Dining</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
+          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Slate Auto</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
+          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior AI Engineer I - Global Dining</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
+          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tree Top</t>
+          <t>Slate Auto</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Selah, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
+          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Snowflake, NoSQL, dbt, CI/CD, Jenkins, Maven, Docker</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae4f189101c570b8</t>
+          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
+          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Tree Top</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Selah, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,42 +2271,42 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
+          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SMTS IT Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
+          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Solution Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
+          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, iCasino</t>
+          <t>SMTS IT Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer - Airflow</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Senior Software Engineer, iCasino</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
+          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Customer Reliability Engineer - Airflow</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
+          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Research Informatics</t>
+          <t>Java AWS Software Engineer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mammoth Biosciences</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Newark, DE, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
+          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Software Engineer I, Research Informatics</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Mammoth Biosciences</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Agentic AI Engineering Architect (Remote -US)</t>
+          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
+          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>K Tech International</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Torrington, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,112 +2726,112 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
+          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
+          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Agentic AI Engineering Architect (Remote -US)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ROYAL ELECTRIC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
+          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
+          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>K Tech International</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Torrington, CT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
+          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
+          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>ROYAL ELECTRIC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
+          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
+          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
+          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer (Implementation &amp; Integration)</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Meduit</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer III</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
+          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer (Implementation &amp; Integration)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Elm &amp; Oak Health</t>
+          <t>Meduit</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Application Developer/Programmer II</t>
+          <t>Data Warehouse Software Engineer III</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Associated Grocers of New England, Inc.</t>
+          <t>Babel Street</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pembroke, NH, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
+          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
+          <t>Senior PowerBI Developer (FDOT OOC)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>TECKpert</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
+          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Level Data, Inc</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform Infrastructure</t>
+          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SmarterDx</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,15 +3566,225 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Sr Data Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Milwaukee Tool</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Menomonee Falls, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Elm &amp; Oak Health</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Rochester, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>New Relic</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>DevOps Engineer II</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Level Data, Inc</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Application Developer/Programmer II</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Associated Grocers of New England, Inc.</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Pembroke, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Platform Infrastructure</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SmarterDx</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
           <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
         </is>

--- a/results/job_matches_2026-08-15.xlsx
+++ b/results/job_matches_2026-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G96"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Java AWS Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>talent source global</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, BigQuery, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4deff5096edc72f7</t>
+          <t>https://www.indeed.com/viewjob?jk=356ce32716bcc358</t>
         </is>
       </c>
     </row>
@@ -636,42 +636,42 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356ce32716bcc358</t>
+          <t>https://www.indeed.com/viewjob?jk=88370938985e0439</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Java AWS Developer</t>
+          <t>Data Architect-68464</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88370938985e0439</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a6ef929081a1</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a6ef929081a1</t>
+          <t>https://www.indeed.com/viewjob?jk=9d634d7b84760169</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect-68464</t>
+          <t>Sr Engineer, SRE TechOps CICD (Remote)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d634d7b84760169</t>
+          <t>https://www.indeed.com/viewjob?jk=02946a77bdd7bddf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Engineer, SRE TechOps CICD (Remote)</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02946a77bdd7bddf</t>
+          <t>https://www.indeed.com/viewjob?jk=4473ab579b8e449a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (API Integrations)</t>
+          <t>Scientific Technical Engineer - PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4473ab579b8e449a</t>
+          <t>https://www.indeed.com/viewjob?jk=097744a388fc20c6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Scientific Technical Engineer - PDS&amp;T CMC</t>
+          <t>Senior Data Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,24 +836,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097744a388fc20c6</t>
+          <t>https://www.indeed.com/viewjob?jk=d460a6aac4fd260a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (On-Site)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d460a6aac4fd260a</t>
+          <t>https://www.indeed.com/viewjob?jk=afe1d38414cdf113</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,24 +906,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe1d38414cdf113</t>
+          <t>https://www.indeed.com/viewjob?jk=986170411aab2db0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Sr. Engineer II, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986170411aab2db0</t>
+          <t>https://www.indeed.com/viewjob?jk=e33354ecb78e1f09</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Engineer II, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33354ecb78e1f09</t>
+          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Technical Software Engineer</t>
+          <t>Full Stack Developer [development, QA automation, data]</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,69 +1011,69 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
+          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Full Stack Developer [development, QA automation, data]</t>
+          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
+          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
+          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>GCP Architect Grade C2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
+          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GCP Architect Grade C2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Delaware Nation Industries</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Delaware Nation Industries</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
+          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
+          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
+          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mid- Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer, Global</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
+          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
+          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
         </is>
       </c>
     </row>
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
+          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,19 +1581,19 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Senior Site Reliability Engineer NEX</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Patterson-UTI Drilling Company LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
+          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer NEX</t>
+          <t>Data Modeling &amp; AI Analytics</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Patterson-UTI Drilling Company LLC</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
+          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Modeling &amp; AI Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Pharmacy Data Management, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Poland, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
+          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MQ Architect</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pharmacy Data Management, Inc.</t>
+          <t>CloudSecurityweb</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
+          <t>https://www.indeed.com/viewjob?jk=523220d0e85b6be6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MQ Architect</t>
+          <t>Software Engineer - Digital Site Development</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CloudSecurityweb</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523220d0e85b6be6</t>
+          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer - Digital Site Development</t>
+          <t>Senior Cloud Engineering Architect - Evinova</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4e06659b43811d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineering Architect - Evinova</t>
+          <t>Software Engineer II - AI/ML Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Kafka, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4e06659b43811d</t>
+          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML Developer</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>QA Software Engineer NC Hybrid</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>QA Software Engineer NC Hybrid</t>
+          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
+          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>True Zero Technologies</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>True Zero Technologies</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
+          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
+          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior AI Engineer I - Global Dining</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
+          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior AI Engineer I - Global Dining</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Slate Auto</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
+          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Slate Auto</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
+          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tree Top</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Selah, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
+          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tree Top</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Selah, WA, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
+          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Solution Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
+          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>SMTS IT Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
+          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SMTS IT Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Senior Software Engineer, iCasino</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
+          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, iCasino</t>
+          <t>Customer Reliability Engineer - Airflow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer - Airflow</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Java AWS Software Engineer III</t>
+          <t>Senior Software Engineer I, Research Informatics</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mammoth Biosciences</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Newark, DE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, RDS, Databricks, Spark, Scala, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8275b35f957f4f39</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
+          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Research Informatics</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Mammoth Biosciences</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
+          <t>Agentic AI Engineering Architect (Remote -US)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
+          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
+          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
         </is>
       </c>
     </row>
@@ -2813,17 +2813,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Agentic AI Engineering Architect (Remote -US)</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
+          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>K Tech International</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Torrington, CT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>K Tech International</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Torrington, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,19 +2946,19 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
+          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
+          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>ROYAL ELECTRIC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,19 +3016,19 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
+          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ROYAL ELECTRIC</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
+          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Data Engineer (Implementation &amp; Integration)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Meduit</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Data Warehouse Software Engineer III</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Babel Street</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
+          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer (Implementation &amp; Integration)</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Meduit</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer III</t>
+          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior PowerBI Developer (FDOT OOC)</t>
+          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TECKpert</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
+          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Senior PowerBI Developer (FDOT OOC)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>TECKpert</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
+          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Elm &amp; Oak Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
+          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Elm &amp; Oak Health</t>
+          <t>Level Data, Inc</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
+          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
+          <t>Application Developer/Programmer II</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>Associated Grocers of New England, Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Pembroke, NH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Senior Software Engineer, Platform Infrastructure</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Level Data, Inc</t>
+          <t>SmarterDx</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3715,76 +3715,6 @@
         </is>
       </c>
       <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Application Developer/Programmer II</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Associated Grocers of New England, Inc.</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Pembroke, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Platform Infrastructure</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>SmarterDx</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
         </is>

--- a/results/job_matches_2026-08-15.xlsx
+++ b/results/job_matches_2026-08-15.xlsx
@@ -748,25 +748,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (API Integrations)</t>
+          <t>Scientific Technical Engineer - PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4473ab579b8e449a</t>
+          <t>https://www.indeed.com/viewjob?jk=097744a388fc20c6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Scientific Technical Engineer - PDS&amp;T CMC</t>
+          <t>Senior Data Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,24 +801,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097744a388fc20c6</t>
+          <t>https://www.indeed.com/viewjob?jk=d460a6aac4fd260a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (On-Site)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d460a6aac4fd260a</t>
+          <t>https://www.indeed.com/viewjob?jk=afe1d38414cdf113</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,24 +871,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe1d38414cdf113</t>
+          <t>https://www.indeed.com/viewjob?jk=986170411aab2db0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Sr. Engineer II, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986170411aab2db0</t>
+          <t>https://www.indeed.com/viewjob?jk=e33354ecb78e1f09</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Engineer II, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Full Stack Developer [development, QA automation, data]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
+          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33354ecb78e1f09</t>
+          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
         </is>
       </c>
     </row>
@@ -993,52 +993,52 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Full Stack Developer [development, QA automation, data]</t>
+          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
+          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
+          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>GCP Architect Grade C2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
+          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GCP Architect Grade C2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Delaware Nation Industries</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Delaware Nation Industries</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
+          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
+          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
+          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mid- Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer, Global</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
+          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
+          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
         </is>
       </c>
     </row>
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
+          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Senior Site Reliability Engineer NEX</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Patterson-UTI Drilling Company LLC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
+          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer NEX</t>
+          <t>Data Modeling &amp; AI Analytics</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Patterson-UTI Drilling Company LLC</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
+          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Modeling &amp; AI Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Pharmacy Data Management, Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Poland, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
+          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II - AI/ML Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pharmacy Data Management, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
+          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MQ Architect</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CloudSecurityweb</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=523220d0e85b6be6</t>
+          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
         </is>
       </c>
     </row>
@@ -1798,25 +1798,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML Developer</t>
+          <t>QA Software Engineer NC Hybrid</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,59 +1826,59 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
+          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>QA Software Engineer NC Hybrid</t>
+          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>True Zero Technologies</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
+          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>True Zero Technologies</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>LevelUp</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
+          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
+          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior AI Engineer I - Global Dining</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
+          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior AI Engineer I - Global Dining</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Slate Auto</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
+          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Slate Auto</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
+          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tree Top</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Selah, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
+          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tree Top</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Selah, WA, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
+          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Solution Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
+          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>SMTS IT Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
+          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SMTS IT Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Senior Software Engineer, iCasino</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
+          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, iCasino</t>
+          <t>Customer Reliability Engineer - Airflow</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer - Airflow</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Senior Software Engineer I, Research Informatics</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Mammoth Biosciences</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Research Informatics</t>
+          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Mammoth Biosciences</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
+          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Agentic AI Engineering Architect (Remote -US)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
+          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Agentic AI Engineering Architect (Remote -US)</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
+          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,17 +2656,17 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
+          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
+          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>K Tech International</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Torrington, CT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>K Tech International</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Torrington, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
+          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
+          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ROYAL ELECTRIC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ROYAL ELECTRIC</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
+          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
+          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
+          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Data Engineer (Implementation &amp; Integration)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Meduit</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer (Implementation &amp; Integration)</t>
+          <t>Data Warehouse Software Engineer III</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Meduit</t>
+          <t>Babel Street</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer III</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
+          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior PowerBI Developer (FDOT OOC)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>TECKpert</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
+          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
+          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior PowerBI Developer (FDOT OOC)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TECKpert</t>
+          <t>Elm &amp; Oak Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Application Developer/Programmer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Elm &amp; Oak Health</t>
+          <t>Associated Grocers of New England, Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Pembroke, NH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
+          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>Law School Admission Council</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Newtown, PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Level Data, Inc</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Application Developer/Programmer II</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Associated Grocers of New England, Inc.</t>
+          <t>Level Data, Inc</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Pembroke, NH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
+          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-15.xlsx
+++ b/results/job_matches_2026-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1973,17 +1973,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LevelUp</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>LevelUp</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
+          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
         </is>
       </c>
     </row>
@@ -2848,17 +2848,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
+          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ROYAL ELECTRIC</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
+          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>ROYAL ELECTRIC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
+          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
+          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
+          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer (Implementation &amp; Integration)</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Meduit</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer III</t>
+          <t>Data Engineer (Implementation &amp; Integration)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>Meduit</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>Data Warehouse Software Engineer III</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Babel Street</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
+          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,14 +3401,14 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
+          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior PowerBI Developer (FDOT OOC)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>TECKpert</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior PowerBI Developer (FDOT OOC)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Elm &amp; Oak Health</t>
+          <t>TECKpert</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
+          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
+          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Application Developer/Programmer II</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Associated Grocers of New England, Inc.</t>
+          <t>Elm &amp; Oak Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pembroke, NH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
+          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Application Developer/Programmer II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Law School Admission Council</t>
+          <t>Associated Grocers of New England, Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Newtown, PA, US USA</t>
+          <t>Pembroke, NH, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>Law School Admission Council</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Newtown, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Level Data, Inc</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform Infrastructure</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SmarterDx</t>
+          <t>Level Data, Inc</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,15 +3706,50 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Platform Infrastructure</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SmarterDx</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
         </is>

--- a/results/job_matches_2026-08-15.xlsx
+++ b/results/job_matches_2026-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack Developer [development, QA automation, data]</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
+          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Technical Software Engineer</t>
+          <t>Full Stack Developer [development, QA automation, data]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
+          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
         </is>
       </c>
     </row>
@@ -1098,25 +1098,25 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GCP Architect Grade C2</t>
+          <t>Senior Identity &amp; Access Management (CIAM) Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
+          <t>https://www.indeed.com/viewjob?jk=b50d50511fbcccef</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Architect Grade C2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Delaware Nation Industries</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Delaware Nation Industries</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
+          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
+          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
+          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Product Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer, Global</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Mid- Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
+          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
+          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
         </is>
       </c>
     </row>
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
+          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer NEX</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Patterson-UTI Drilling Company LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Modeling &amp; AI Analytics</t>
+          <t>Senior Site Reliability Engineer NEX</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Patterson-UTI Drilling Company LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
+          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Modeling &amp; AI Analytics</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pharmacy Data Management, Inc.</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
+          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
+          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Pharmacy Data Management, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Poland, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,24 +1676,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
+          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Software Engineer II - AI/ML Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer - Digital Site Development</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
+          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineering Architect - Evinova</t>
+          <t>Software Engineer - Digital Site Development</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Kafka, ETL, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4e06659b43811d</t>
+          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QA Software Engineer NC Hybrid</t>
+          <t>Senior Cloud Engineering Architect - Evinova</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>AstraZeneca</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Gaithersburg, MD, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Kafka, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4e06659b43811d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
+          <t>QA Software Engineer NC Hybrid</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
+          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
+          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>True Zero Technologies</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>True Zero Technologies</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
+          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LevelUp</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,69 +2026,69 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
+          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior AI Engineer I - Global Dining</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>LevelUp</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
+          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior AI Engineer I - Global Dining</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Slate Auto</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Slate Auto</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
+          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
+          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tree Top</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Selah, WA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
+          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Tree Top</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Selah, WA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
+          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
+          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SMTS IT Engineer</t>
+          <t>Solution Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
+          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>SMTS IT Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
+          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, iCasino</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer - Airflow</t>
+          <t>Senior Software Engineer, iCasino</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
+          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Customer Reliability Engineer - Airflow</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
+          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Research Informatics</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mammoth Biosciences</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Networking for Future, Inc.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
+          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Software Engineer I, Research Informatics</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Mammoth Biosciences</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Agentic AI Engineering Architect (Remote -US)</t>
+          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
+          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Agentic AI Engineering Architect (Remote -US)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
+          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
+          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
+          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>K Tech International</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Torrington, CT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,42 +2831,42 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
+          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>K Tech International</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Torrington, CT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
         </is>
       </c>
     </row>
@@ -2946,19 +2946,19 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
+          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ROYAL ELECTRIC</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,19 +3016,19 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
+          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
+          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>ROYAL ELECTRIC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
+          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
+          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
+          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer (Implementation &amp; Integration)</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Meduit</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer III</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>Data Engineer (Implementation &amp; Integration)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Meduit</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Data Warehouse Software Engineer III</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Babel Street</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Somerville, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
+          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior PowerBI Developer (FDOT OOC)</t>
+          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>TECKpert</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Elm &amp; Oak Health</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
+          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Application Developer/Programmer II</t>
+          <t>Senior PowerBI Developer (FDOT OOC)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Associated Grocers of New England, Inc.</t>
+          <t>TECKpert</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Pembroke, NH, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
+          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
+          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
         </is>
       </c>
     </row>
@@ -3653,17 +3653,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>Elm &amp; Oak Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Level Data, Inc</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform Infrastructure</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SmarterDx</t>
+          <t>Level Data, Inc</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,15 +3741,85 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Application Developer/Programmer II</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Associated Grocers of New England, Inc.</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Pembroke, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Platform Infrastructure</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SmarterDx</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
         </is>

--- a/results/job_matches_2026-08-15.xlsx
+++ b/results/job_matches_2026-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1798,25 +1798,25 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineering Architect - Evinova</t>
+          <t>QA Software Engineer NC Hybrid</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AstraZeneca</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Gaithersburg, MD, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Scala, Kafka, ETL, CI/CD</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4e06659b43811d</t>
+          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>QA Software Engineer NC Hybrid</t>
+          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
+          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>True Zero Technologies</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>True Zero Technologies</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
+          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>LevelUp</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
+          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
         </is>
       </c>
     </row>
@@ -2043,52 +2043,52 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior AI Engineer I - Global Dining</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>LevelUp</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
+          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior AI Engineer I - Global Dining</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Slate Auto</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
+          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Slate Auto</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
+          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tree Top</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Selah, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
+          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tree Top</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Selah, WA, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
+          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Solution Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
+          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>SMTS IT Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
+          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SMTS IT Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Senior Software Engineer, iCasino</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
+          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, iCasino</t>
+          <t>Customer Reliability Engineer - Airflow</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer - Airflow</t>
+          <t>Data Engineer - Finance AI Solutions</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
+          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>IT Cloud Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
+          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Agentic AI Engineering Architect (Remote -US)</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
+          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,17 +2691,17 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Agentic AI Engineering Architect (Remote -US)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
+          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
+          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
         </is>
       </c>
     </row>
@@ -3443,17 +3443,17 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>Senior PowerBI Developer (FDOT OOC)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>TECKpert</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
+          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
+          <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior PowerBI Developer (FDOT OOC)</t>
+          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>TECKpert</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Law School Admission Council</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Newtown, PA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
+          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
         </is>
       </c>
     </row>
@@ -3688,17 +3688,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>Law School Admission Council</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Newtown, PA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Level Data, Inc</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Application Developer/Programmer II</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Associated Grocers of New England, Inc.</t>
+          <t>Level Data, Inc</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Pembroke, NH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
+          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform Infrastructure</t>
+          <t>Application Developer/Programmer II</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SmarterDx</t>
+          <t>Associated Grocers of New England, Inc.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pembroke, NH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,15 +3811,50 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Platform Infrastructure</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SmarterDx</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
           <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
         </is>

--- a/results/job_matches_2026-08-15.xlsx
+++ b/results/job_matches_2026-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,105 +468,105 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Databricks Solution Architect - Onsite- W2</t>
+          <t>SR Azure Data Factory- Remote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.9</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Data Lake Storage, Unity Catalog, Delta Live Tables, Google Cloud Platform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7af5960a321f1aa</t>
+          <t>https://www.indeed.com/viewjob?jk=9d8625d99e5c7e4a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SR Azure Data Factory- Remote</t>
+          <t>Hadoop Solutions Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d8625d99e5c7e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e611db79889b1d9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hadoop Solutions Developer</t>
+          <t>Senior Java AWS Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.8</v>
+        <v>20.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e611db79889b1d9</t>
+          <t>https://www.indeed.com/viewjob?jk=356ce32716bcc358</t>
         </is>
       </c>
     </row>
@@ -601,42 +601,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356ce32716bcc358</t>
+          <t>https://www.indeed.com/viewjob?jk=88370938985e0439</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Java AWS Developer</t>
+          <t>Data Architect-68464</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Hitachi Energy</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Reading, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88370938985e0439</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c2a6ef929081a1</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>Hitachi Rail</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a6ef929081a1</t>
+          <t>https://www.indeed.com/viewjob?jk=9d634d7b84760169</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Architect-68464</t>
+          <t>Sr Engineer, SRE TechOps CICD (Remote)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d634d7b84760169</t>
+          <t>https://www.indeed.com/viewjob?jk=02946a77bdd7bddf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Engineer, SRE TechOps CICD (Remote)</t>
+          <t>Scientific Technical Engineer - PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02946a77bdd7bddf</t>
+          <t>https://www.indeed.com/viewjob?jk=097744a388fc20c6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Scientific Technical Engineer - PDS&amp;T CMC</t>
+          <t>Senior Data Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,24 +766,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097744a388fc20c6</t>
+          <t>https://www.indeed.com/viewjob?jk=d460a6aac4fd260a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (On-Site)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d460a6aac4fd260a</t>
+          <t>https://www.indeed.com/viewjob?jk=afe1d38414cdf113</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,24 +836,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe1d38414cdf113</t>
+          <t>https://www.indeed.com/viewjob?jk=986170411aab2db0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Sr. Engineer II, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986170411aab2db0</t>
+          <t>https://www.indeed.com/viewjob?jk=e33354ecb78e1f09</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Engineer II, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33354ecb78e1f09</t>
+          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Technical Software Engineer</t>
+          <t>Full Stack Developer [development, QA automation, data]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,69 +941,69 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
+          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full Stack Developer [development, QA automation, data]</t>
+          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
+          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
+          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Identity &amp; Access Management (CIAM) Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
+          <t>https://www.indeed.com/viewjob?jk=b50d50511fbcccef</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Identity &amp; Access Management (CIAM) Engineer</t>
+          <t>GCP Architect Grade C2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50d50511fbcccef</t>
+          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GCP Architect Grade C2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Delaware Nation Industries</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Delaware Nation Industries</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
+          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
+          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1331,29 +1331,29 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr Product Software Engineer</t>
+          <t>Mid- Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, ECS, Databricks, Spark, Scala, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56a93ae153035d32</t>
+          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer, Global</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
+          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
+          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Senior Site Reliability Engineer NEX</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Patterson-UTI Drilling Company LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Data Modeling &amp; AI Analytics</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
+          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer NEX</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Patterson-UTI Drilling Company LLC</t>
+          <t>Pharmacy Data Management, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Poland, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
+          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Modeling &amp; AI Analytics</t>
+          <t>Software Engineer II - AI/ML Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
+          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pharmacy Data Management, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
+          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML Developer</t>
+          <t>Software Engineer - Digital Site Development</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
+          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>QA Software Engineer NC Hybrid</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,59 +1756,59 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer - Digital Site Development</t>
+          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QA Software Engineer NC Hybrid</t>
+          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>True Zero Technologies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
+          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>True Zero Technologies</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>LevelUp</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
+          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
+          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior AI Engineer I - Global Dining</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LevelUp</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
+          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>Slate Auto</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
+          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior AI Engineer I - Global Dining</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
+          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Slate Auto</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Tree Top</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Selah, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
+          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
+          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Solution Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tree Top</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Selah, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
+          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>SMTS IT Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
+          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SMTS IT Engineer</t>
+          <t>Senior Software Engineer, iCasino</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
+          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Customer Reliability Engineer - Airflow</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Astronomer</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Boston, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
+          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, iCasino</t>
+          <t>IT Cloud Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer - Airflow</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>Networking for Future, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
+          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer - Finance AI Solutions</t>
+          <t>Senior Software Engineer I, Research Informatics</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Mammoth Biosciences</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, PySpark, Scala, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f6056b3749eea65</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer II</t>
+          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Networking for Future, Inc.</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Research Informatics</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mammoth Biosciences</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
+          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
+          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
+          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,19 +2666,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Agentic AI Engineering Architect (Remote -US)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
+          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
+          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
+          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Agentic AI Engineering Architect (Remote -US)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>K Tech International</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Torrington, CT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,19 +2806,19 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2827,11 +2827,11 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>K Tech International</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Torrington, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
+          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
+          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>ROYAL ELECTRIC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
+          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
+          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>ROYAL ELECTRIC</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
+          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Data Engineer (Implementation &amp; Integration)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Meduit</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior PowerBI Developer (FDOT OOC)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>TECKpert</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
+          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
+          <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer (Implementation &amp; Integration)</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Meduit</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer III</t>
+          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Cloud Storage, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e34dd82bc09fa105</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior PowerBI Developer (FDOT OOC)</t>
+          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TECKpert</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
+          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Elm &amp; Oak Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
+          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Law School Admission Council</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Newtown, PA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
+          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Level Data, Inc</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
+          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Application Developer/Programmer II</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Elm &amp; Oak Health</t>
+          <t>Associated Grocers of New England, Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Pembroke, NH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
+          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer, Platform Infrastructure</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Law School Admission Council</t>
+          <t>SmarterDx</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Newtown, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3715,146 +3715,6 @@
         </is>
       </c>
       <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>New Relic</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>DevOps Engineer II</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Level Data, Inc</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Application Developer/Programmer II</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Associated Grocers of New England, Inc.</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Pembroke, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Platform Infrastructure</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>SmarterDx</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
         </is>

--- a/results/job_matches_2026-08-15.xlsx
+++ b/results/job_matches_2026-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Technical Software Engineer</t>
+          <t>Full Stack Developer [development, QA automation, data]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
+          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack Developer [development, QA automation, data]</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
+          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
         </is>
       </c>
     </row>
@@ -2533,17 +2533,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Agentic AI Engineering Architect (Remote -US)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
+          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
+          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
+          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Agentic AI Engineering Architect (Remote -US)</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
+          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,17 +2726,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
         </is>
       </c>
     </row>
@@ -3303,17 +3303,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior PowerBI Developer (FDOT OOC)</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TECKpert</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
+          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
+          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
+          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Senior PowerBI Developer (FDOT OOC)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>TECKpert</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
+          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
+          <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
         </is>
       </c>
     </row>
@@ -3548,17 +3548,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Application Developer/Programmer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Law School Admission Council</t>
+          <t>Associated Grocers of New England, Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Newtown, PA, US USA</t>
+          <t>Pembroke, NH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
+          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
+          <t>Senior Software Engineer, Platform Infrastructure</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>SmarterDx</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
+          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Level Data, Inc</t>
+          <t>Law School Admission Council</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Newtown, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
+          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Application Developer/Programmer II</t>
+          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Associated Grocers of New England, Inc.</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Pembroke, NH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform Infrastructure</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SmarterDx</t>
+          <t>Level Data, Inc</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,7 +3716,42 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
+          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Waystar</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-15.xlsx
+++ b/results/job_matches_2026-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,52 +713,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Scientific Technical Engineer - PDS&amp;T CMC</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, RDS, Spark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097744a388fc20c6</t>
+          <t>https://www.indeed.com/viewjob?jk=37b325f2f84b39b8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (On-Site)</t>
+          <t>Scientific Technical Engineer - PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,24 +766,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d460a6aac4fd260a</t>
+          <t>https://www.indeed.com/viewjob?jk=097744a388fc20c6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe1d38414cdf113</t>
+          <t>https://www.indeed.com/viewjob?jk=d460a6aac4fd260a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,24 +836,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
+          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986170411aab2db0</t>
+          <t>https://www.indeed.com/viewjob?jk=afe1d38414cdf113</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Engineer II, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33354ecb78e1f09</t>
+          <t>https://www.indeed.com/viewjob?jk=986170411aab2db0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack Developer [development, QA automation, data]</t>
+          <t>Sr. Engineer II, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
+          <t>https://www.indeed.com/viewjob?jk=e33354ecb78e1f09</t>
         </is>
       </c>
     </row>
@@ -958,52 +958,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
+          <t>Full Stack Developer [development, QA automation, data]</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
+          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
+          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Identity &amp; Access Management (CIAM) Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50d50511fbcccef</t>
+          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GCP Architect Grade C2</t>
+          <t>Senior Identity &amp; Access Management (CIAM) Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
+          <t>https://www.indeed.com/viewjob?jk=b50d50511fbcccef</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Architect Grade C2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Delaware Nation Industries</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Delaware Nation Industries</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
+          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
+          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1331,29 +1331,29 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer, Global</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Mid- Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
+          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Campbell's</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
+          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
         </is>
       </c>
     </row>
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,19 +1511,19 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
+          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer NEX</t>
+          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Patterson-UTI Drilling Company LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Modeling &amp; AI Analytics</t>
+          <t>Senior Site Reliability Engineer NEX</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Patterson-UTI Drilling Company LLC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
+          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Modeling &amp; AI Analytics</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pharmacy Data Management, Inc.</t>
+          <t>Matrix International Financial Services</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
+          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
+          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Pharmacy Data Management, Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Poland, OH, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,24 +1641,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
+          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Software Engineer II - AI/ML Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer - Digital Site Development</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
+          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QA Software Engineer NC Hybrid</t>
+          <t>Software Engineer - Digital Site Development</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
+          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
+          <t>QA Software Engineer NC Hybrid</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
+          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
+          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>True Zero Technologies</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>True Zero Technologies</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
+          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LevelUp</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>LevelUp</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,42 +1956,42 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
+          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior AI Engineer I - Global Dining</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
+          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior AI Engineer I - Global Dining</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Slate Auto</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Slate Auto</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
+          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
+          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tree Top</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Selah, WA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
+          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Tree Top</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Selah, WA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
+          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
+          <t>S3, RDS, Cloud Storage, Snowflake, NoSQL, dbt, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
+          <t>https://www.indeed.com/viewjob?jk=ae4f189101c570b8</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SMTS IT Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
+          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Solution Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
+          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, iCasino</t>
+          <t>SMTS IT Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Customer Reliability Engineer - Airflow</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Astronomer</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Boston, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, GCP, Snowflake, PostgreSQL, dbt, DataOps, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e441a087ab697b63</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer II</t>
+          <t>Senior Software Engineer, iCasino</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>IT Cloud Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Networking for Future, Inc.</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
+          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Research Informatics</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mammoth Biosciences</t>
+          <t>Networking for Future, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
+          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
+          <t>Senior Software Engineer I, Research Informatics</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Mammoth Biosciences</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
+          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
+          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Agentic AI Engineering Architect (Remote -US)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,17 +2586,17 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
+          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Biostatician</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
+          <t>https://www.indeed.com/viewjob?jk=aa3a4edd24420508</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Agentic AI Engineering Architect (Remote -US)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>K Tech International</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Torrington, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
+          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
+          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>K Tech International</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Torrington, CT, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
         </is>
       </c>
     </row>
@@ -2911,19 +2911,19 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
+          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ROYAL ELECTRIC</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,19 +2981,19 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
+          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
+          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>ROYAL ELECTRIC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
+          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
+          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
+          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer (Implementation &amp; Integration)</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Meduit</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Data Engineer (Implementation &amp; Integration)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Meduit</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Senior PowerBI Developer (FDOT OOC)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>TECKpert</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
+          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
+          <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior PowerBI Developer (FDOT OOC)</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TECKpert</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
+          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Elm &amp; Oak Health</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
+          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Application Developer/Programmer II</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Associated Grocers of New England, Inc.</t>
+          <t>Elm &amp; Oak Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pembroke, NH, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
+          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform Infrastructure</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SmarterDx</t>
+          <t>Law School Admission Council</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newtown, PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
+          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Law School Admission Council</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Newtown, PA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>Level Data, Inc</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Level Data, Inc</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
+          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer, Platform Infrastructure</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>SmarterDx</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,77 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
+          <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Application Developer/Programmer II</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Associated Grocers of New England, Inc.</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Pembroke, NH, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Sr Data Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Milwaukee Tool</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Menomonee Falls, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-15.xlsx
+++ b/results/job_matches_2026-08-15.xlsx
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Modeling &amp; AI Analytics</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Matrix International Financial Services</t>
+          <t>Pharmacy Data Management, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Poland, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Redshift, IAM, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da0b9d9f202b441a</t>
+          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II - AI/ML Developer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pharmacy Data Management, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,24 +1641,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
+          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML Developer</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Software Engineer - Digital Site Development</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer - Digital Site Development</t>
+          <t>QA Software Engineer NC Hybrid</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
+          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QA Software Engineer NC Hybrid</t>
+          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
+          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>True Zero Technologies</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>True Zero Technologies</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
+          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
+          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
         </is>
       </c>
     </row>
@@ -1973,25 +1973,25 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior AI Engineer I - Global Dining</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
+          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AI Engineer I - Global Dining</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Slate Auto</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
+          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Power BI Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Slate Auto</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
+          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tree Top</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Selah, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
+          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tree Top</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Selah, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
+          <t>S3, RDS, Cloud Storage, Snowflake, NoSQL, dbt, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
+          <t>https://www.indeed.com/viewjob?jk=ae4f189101c570b8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Snowflake, NoSQL, dbt, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae4f189101c570b8</t>
+          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Solution Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
+          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>SMTS IT Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
+          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SMTS IT Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Senior Software Engineer, iCasino</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
+          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, iCasino</t>
+          <t>IT Cloud Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer II</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>Networking for Future, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>Senior Software Engineer I, Research Informatics</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Networking for Future, Inc.</t>
+          <t>Mammoth Biosciences</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Research Informatics</t>
+          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mammoth Biosciences</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
+          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
+          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
+          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Biostatician</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
+          <t>https://www.indeed.com/viewjob?jk=aa3a4edd24420508</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Biostatician</t>
+          <t>Agentic AI Engineering Architect (Remote -US)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa3a4edd24420508</t>
+          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Agentic AI Engineering Architect (Remote -US)</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
+          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>K Tech International</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Torrington, CT, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>K Tech International</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Torrington, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
+          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
+          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
+          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ROYAL ELECTRIC</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ROYAL ELECTRIC</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
+          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
+          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
+          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Data Engineer (Implementation &amp; Integration)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Meduit</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer (Implementation &amp; Integration)</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Meduit</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
         </is>
       </c>
     </row>
@@ -3723,17 +3723,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Platform Infrastructure</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SmarterDx</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
+          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
         </is>
       </c>
     </row>
@@ -3793,17 +3793,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer, Platform Infrastructure</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>SmarterDx</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
+          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
+          <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-15.xlsx
+++ b/results/job_matches_2026-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2043,17 +2043,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Power BI Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Dataflow, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c24a02e2aa89d624</t>
+          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tree Top</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Selah, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
+          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tree Top</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Selah, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
+          <t>S3, RDS, Cloud Storage, Snowflake, NoSQL, dbt, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
+          <t>https://www.indeed.com/viewjob?jk=ae4f189101c570b8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Snowflake, NoSQL, dbt, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae4f189101c570b8</t>
+          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Solution Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
+          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>SMTS IT Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
+          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SMTS IT Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Senior Software Engineer, iCasino</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
+          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, iCasino</t>
+          <t>IT Cloud Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer II</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>Networking for Future, Inc.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>Senior Software Engineer I, Research Informatics</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Networking for Future, Inc.</t>
+          <t>Mammoth Biosciences</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Research Informatics</t>
+          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mammoth Biosciences</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
+          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Agentic AI Engineering Architect (Remote -US)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
+          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
+          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
+          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
+          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Biostatician</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, SQL Server, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa3a4edd24420508</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Agentic AI Engineering Architect (Remote -US)</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
+          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>K Tech International</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Torrington, CT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>K Tech International</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Torrington, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
         </is>
       </c>
     </row>
@@ -2876,19 +2876,19 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
+          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
+          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>ROYAL ELECTRIC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,19 +2946,19 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
+          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ROYAL ELECTRIC</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
+          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Data Engineer (Implementation &amp; Integration)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Meduit</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer (Implementation &amp; Integration)</t>
+          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Meduit</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior PowerBI Developer (FDOT OOC)</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TECKpert</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
+          <t>Senior PowerBI Developer (FDOT OOC)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>TECKpert</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
+          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
+          <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Elm &amp; Oak Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
+          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Law School Admission Council</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Newtown, PA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
+          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Elm &amp; Oak Health</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Law School Admission Council</t>
+          <t>Level Data, Inc</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Newtown, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
+          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Level Data, Inc</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
+          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Application Developer/Programmer II</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Associated Grocers of New England, Inc.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Pembroke, NH, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
+          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Software Engineer, Platform Infrastructure</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>SmarterDx</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
+          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3750,76 +3750,6 @@
         </is>
       </c>
       <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Application Developer/Programmer II</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Associated Grocers of New England, Inc.</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Pembroke, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Platform Infrastructure</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>SmarterDx</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
         </is>

--- a/results/job_matches_2026-08-15.xlsx
+++ b/results/job_matches_2026-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,25 +643,25 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Architect-68464</t>
+          <t>Sr Engineer, SRE TechOps CICD (Remote)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hitachi Rail</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,94 +671,94 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d634d7b84760169</t>
+          <t>https://www.indeed.com/viewjob?jk=02946a77bdd7bddf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr Engineer, SRE TechOps CICD (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, RDS, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02946a77bdd7bddf</t>
+          <t>https://www.indeed.com/viewjob?jk=37b325f2f84b39b8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Scientific Technical Engineer - PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>North Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, RDS, Spark</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b325f2f84b39b8</t>
+          <t>https://www.indeed.com/viewjob?jk=097744a388fc20c6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Scientific Technical Engineer - PDS&amp;T CMC</t>
+          <t>Senior Data Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,24 +766,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097744a388fc20c6</t>
+          <t>https://www.indeed.com/viewjob?jk=d460a6aac4fd260a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (On-Site)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d460a6aac4fd260a</t>
+          <t>https://www.indeed.com/viewjob?jk=afe1d38414cdf113</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,24 +836,24 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe1d38414cdf113</t>
+          <t>https://www.indeed.com/viewjob?jk=986170411aab2db0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Sr. Engineer II, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986170411aab2db0</t>
+          <t>https://www.indeed.com/viewjob?jk=e33354ecb78e1f09</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Engineer II, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Full Stack Developer [development, QA automation, data]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
+          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33354ecb78e1f09</t>
+          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
         </is>
       </c>
     </row>
@@ -958,52 +958,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Full Stack Developer [development, QA automation, data]</t>
+          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
+          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
+          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Senior Identity &amp; Access Management (CIAM) Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
+          <t>https://www.indeed.com/viewjob?jk=b50d50511fbcccef</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Identity &amp; Access Management (CIAM) Engineer</t>
+          <t>GCP Architect Grade C2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50d50511fbcccef</t>
+          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GCP Architect Grade C2</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>R.S. Hughes Company, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
+          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Delaware Nation Industries</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Delaware Nation Industries</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
+          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
+          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1331,29 +1331,29 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mid- Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer, Global</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
+          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Campbell's</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Medallion Architecture, Spark, Scala, Data Modeling, ETL</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20897d728ad2b031</t>
+          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Senior Site Reliability Engineer NEX</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Patterson-UTI Drilling Company LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Pharmacy Data Management, Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Poland, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,24 +1501,24 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Databricks, Python / Java</t>
+          <t>Software Engineer II - AI/ML Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bb89514a86b7c54</t>
+          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer NEX</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Patterson-UTI Drilling Company LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Digital Site Development</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pharmacy Data Management, Inc.</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,42 +1606,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
+          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML Developer</t>
+          <t>QA Software Engineer NC Hybrid</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
+          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer - Digital Site Development</t>
+          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>True Zero Technologies</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QA Software Engineer NC Hybrid</t>
+          <t>DATA ENGINEER I</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>United States Cold Storage</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Camden, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
+          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>True Zero Technologies</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
+          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>LevelUp</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,42 +1851,42 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
+          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Slate Auto</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
+          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,59 +1931,59 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
+          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LevelUp</t>
+          <t>Tree Top</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Selah, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
+          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior AI Engineer I - Global Dining</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>SailPoint Technologies</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Hadoop, Spark, Scala, Kafka, ETL, MLOps, CI/CD</t>
+          <t>S3, RDS, Cloud Storage, Snowflake, NoSQL, dbt, CI/CD, Jenkins, Maven, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=891a966c96f6d006</t>
+          <t>https://www.indeed.com/viewjob?jk=ae4f189101c570b8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Slate Auto</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Solution Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,67 +2071,67 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
+          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>SMTS IT Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tree Top</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Selah, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
+          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>ISPOT</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Snowflake, NoSQL, dbt, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae4f189101c570b8</t>
+          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer, iCasino</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Penn Interactive Ventures</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
+          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>IT Cloud Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
+          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SMTS IT Engineer</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Networking for Future, Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
+          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Senior Software Engineer I, Research Informatics</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>Mammoth Biosciences</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, iCasino</t>
+          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer II</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Networking for Future, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
+          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Research Informatics</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Mammoth Biosciences</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
+          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
+          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
         </is>
       </c>
     </row>
@@ -2568,17 +2568,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>K Tech International</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Torrington, CT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,112 +2621,112 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
+          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
+          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>K Tech International</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Torrington, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
+          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>ROYAL ELECTRIC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,19 +2806,19 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
+          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ROYAL ELECTRIC</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
+          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Data Engineer (Implementation &amp; Integration)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Meduit</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
+          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior PowerBI Developer (FDOT OOC)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>TECKpert</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
+          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
+          <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer (Implementation &amp; Integration)</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Meduit</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
+          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Application Developer/Programmer II</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Associated Grocers of New England, Inc.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Pembroke, NH, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
+          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>Elm &amp; Oak Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior PowerBI Developer (FDOT OOC)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TECKpert</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Law School Admission Council</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Newtown, PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
+          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Elm &amp; Oak Health</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Law School Admission Council</t>
+          <t>Level Data, Inc</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Newtown, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
+          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>New Relic</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
+          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>DevOps Engineer II</t>
+          <t>Senior Software Engineer, Platform Infrastructure</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Level Data, Inc</t>
+          <t>SmarterDx</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3610,146 +3610,6 @@
         </is>
       </c>
       <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Waystar</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Milwaukee Tool</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Menomonee Falls, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Application Developer/Programmer II</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Associated Grocers of New England, Inc.</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Pembroke, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Platform Infrastructure</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>SmarterDx</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
         </is>

--- a/results/job_matches_2026-08-15.xlsx
+++ b/results/job_matches_2026-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect-68464</t>
+          <t>Sr Engineer, SRE TechOps CICD (Remote)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Hitachi Energy</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Reading, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Redshift, S3, RDS, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c2a6ef929081a1</t>
+          <t>https://www.indeed.com/viewjob?jk=02946a77bdd7bddf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Engineer, SRE TechOps CICD (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, RDS, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02946a77bdd7bddf</t>
+          <t>https://www.indeed.com/viewjob?jk=37b325f2f84b39b8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Databricks</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Colas</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, RDS, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Time Travel</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b325f2f84b39b8</t>
+          <t>https://www.indeed.com/viewjob?jk=623e6ba410872463</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack Developer [development, QA automation, data]</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
+          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Technical Software Engineer</t>
+          <t>Full Stack Developer [development, QA automation, data]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
+          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
         </is>
       </c>
     </row>
@@ -1168,25 +1168,25 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Delaware Nation Industries</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, Splunk</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=186e1b06b60d4c75</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
+          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
+          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1296,29 +1296,29 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mid- Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer, Global</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
+          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
         </is>
       </c>
     </row>
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
+          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Senior Site Reliability Engineer NEX</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Patterson-UTI Drilling Company LLC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer NEX</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Patterson-UTI Drilling Company LLC</t>
+          <t>Pharmacy Data Management, Inc.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Poland, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
+          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Digital Site Development</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pharmacy Data Management, Inc.</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,17 +1501,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
+          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
         </is>
       </c>
     </row>
@@ -1588,25 +1588,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer - Digital Site Development</t>
+          <t>QA Software Engineer NC Hybrid</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
+          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QA Software Engineer NC Hybrid</t>
+          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
+          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>True Zero Technologies</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>True Zero Technologies</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DATA ENGINEER I</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>United States Cold Storage</t>
+          <t>LevelUp</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Camden, NJ, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8092db12dbdd54c</t>
+          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
+          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>Slate Auto</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,59 +1826,59 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
+          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>LevelUp</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
+          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Solution Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Slate Auto</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SMTS IT Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32d403b17a686b11</t>
+          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>IT Cloud Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tree Top</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Selah, WA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, Azure, GCP, Scala, Azure Cosmos DB, CI/CD</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a50064736e270364</t>
+          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SailPoint Technologies</t>
+          <t>Networking for Future, Inc.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>S3, RDS, Cloud Storage, Snowflake, NoSQL, dbt, CI/CD, Jenkins, Maven, Docker</t>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ae4f189101c570b8</t>
+          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer I, Research Informatics</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Mammoth Biosciences</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
+          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SMTS IT Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Agentic AI Engineering Architect (Remote -US)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ISPOT</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, MySQL, ELT, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba2bc4f8478f2f52</t>
+          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, iCasino</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Penn Interactive Ventures</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, ECS, RDS, Scala, Kafka, PostgreSQL, MySQL, Kubernetes</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86920378643e1b3d</t>
+          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer II</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Networking for Future, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
+          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Research Informatics</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mammoth Biosciences</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
+          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Frontend Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Dresser Utility Solutions</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,182 +2341,182 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
+          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
+          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
+          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Agentic AI Engineering Architect (Remote -US)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>ROYAL ELECTRIC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
+          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>K Tech International</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Torrington, CT, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, PostgreSQL, MySQL, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b1c6bea8b7cd381</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
+          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ROYAL ELECTRIC</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
+          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior PowerBI Developer (FDOT OOC)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>TECKpert</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
+          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
+          <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Elm &amp; Oak Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
+          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Law School Admission Council</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Newtown, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
+          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer (Implementation &amp; Integration)</t>
+          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Meduit</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Scala, Snowflake, SQL Server, PostgreSQL, MySQL, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bfeab7755a77d7f</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>Level Data, Inc</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior PowerBI Developer (FDOT OOC)</t>
+          <t>Senior Software Engineer, Platform Infrastructure</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>TECKpert</t>
+          <t>SmarterDx</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,402 +3216,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Senior QA Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>VIVA</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Adelphi, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>CrowdStrike</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Application Developer/Programmer II</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Associated Grocers of New England, Inc.</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Pembroke, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, MySQL, ETL, Power BI, Tableau</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b0718b808fb76795</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Elm &amp; Oak Health</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Rochester, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Milwaukee Tool</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Menomonee Falls, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Law School Admission Council</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Newtown, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>New Relic</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>DevOps Engineer II</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Level Data, Inc</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Waystar</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Louisville, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, NoSQL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9817c4c795b73795</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Platform Infrastructure</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>SmarterDx</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-15.xlsx
+++ b/results/job_matches_2026-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Scientific Technical Engineer - PDS&amp;T CMC</t>
+          <t>Senior Data Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,24 +731,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=097744a388fc20c6</t>
+          <t>https://www.indeed.com/viewjob?jk=d460a6aac4fd260a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (On-Site)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d460a6aac4fd260a</t>
+          <t>https://www.indeed.com/viewjob?jk=afe1d38414cdf113</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,24 +801,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, PostgreSQL, DynamoDB</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe1d38414cdf113</t>
+          <t>https://www.indeed.com/viewjob?jk=986170411aab2db0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Sr. Engineer II, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986170411aab2db0</t>
+          <t>https://www.indeed.com/viewjob?jk=e33354ecb78e1f09</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Engineer II, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33354ecb78e1f09</t>
+          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Technical Software Engineer</t>
+          <t>Full Stack Developer [development, QA automation, data]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,69 +906,69 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
+          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack Developer [development, QA automation, data]</t>
+          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
+          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior Identity &amp; Access Management (CIAM) Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
+          <t>https://www.indeed.com/viewjob?jk=b50d50511fbcccef</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>GCP Architect Grade C2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Medallion Architecture, Spark, PySpark, Scala</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bcdb54f17a99717</t>
+          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Identity &amp; Access Management (CIAM) Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50d50511fbcccef</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GCP Architect Grade C2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
+          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R.S. Hughes Company, Inc.</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Medallion Architecture, Spark, PySpark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0b4872f64c2f0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1191,29 +1191,29 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Mid- Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
+          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
+          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer, Global</t>
+          <t>Senior Site Reliability Engineer NEX</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Patterson-UTI Drilling Company LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
+          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Pharmacy Data Management, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Poland, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
+          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Software Engineer - Digital Site Development</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer NEX</t>
+          <t>Software Engineer II - AI/ML Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Patterson-UTI Drilling Company LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
+          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Pharmacy Data Management, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
+          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer - Digital Site Development</t>
+          <t>QA Software Engineer NC Hybrid</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,67 +1511,67 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
+          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML Developer</t>
+          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>True Zero Technologies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QA Software Engineer NC Hybrid</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Nestlé Purina</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
+          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>True Zero Technologies</t>
+          <t>LevelUp</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,42 +1676,42 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
+          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Slate Auto</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
+          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LevelUp</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
+          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Solution Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
+          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>SMTS IT Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Slate Auto</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>IT Cloud Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
+          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Networking for Future, Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
+          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SMTS IT Engineer</t>
+          <t>Senior Software Engineer I, Research Informatics</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Mammoth Biosciences</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer II</t>
+          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Networking for Future, Inc.</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Research Informatics</t>
+          <t>Agentic AI Engineering Architect (Remote -US)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mammoth Biosciences</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
+          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
+          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,29 +2096,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
+          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Agentic AI Engineering Architect (Remote -US)</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
+          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,137 +2211,137 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
+          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
+          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Frontend Software Engineer</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Dresser Utility Solutions</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=653282b3cbc10d6f</t>
+          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>ROYAL ELECTRIC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,19 +2386,19 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
+          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Senior Engineer, IT</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Builders FirstSource</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
+          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ROYAL ELECTRIC</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
+          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
+          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior Platform Engineer - Payrix</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Forward Deployed Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>CoorsTek</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Golden, CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
+          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
+          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Senior PowerBI Developer (FDOT OOC)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>TECKpert</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7b0c0663856b10</t>
+          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
+          <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Law School Admission Council</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Newtown, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
+          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Elm &amp; Oak Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
+          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior PowerBI Developer (FDOT OOC)</t>
+          <t>DevOps Engineer II</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TECKpert</t>
+          <t>Level Data, Inc</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
+          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer, Platform Infrastructure</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Elm &amp; Oak Health</t>
+          <t>SmarterDx</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
+          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,182 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Law School Admission Council</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Newtown, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>New Relic</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>DevOps Engineer II</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Level Data, Inc</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Platform Infrastructure</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>SmarterDx</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Milwaukee Tool</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Menomonee Falls, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-15.xlsx
+++ b/results/job_matches_2026-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,35 +538,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Java AWS Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20.1</v>
+        <v>20.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Synapse Analytics, Google Cloud Platform, GCP, BigQuery, Vertex AI, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=356ce32716bcc358</t>
+          <t>https://www.indeed.com/viewjob?jk=d0d5d92a233a5130</t>
         </is>
       </c>
     </row>
@@ -601,94 +601,94 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88370938985e0439</t>
+          <t>https://www.indeed.com/viewjob?jk=356ce32716bcc358</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr Engineer, SRE TechOps CICD (Remote)</t>
+          <t>Senior Java AWS Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>20.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02946a77bdd7bddf</t>
+          <t>https://www.indeed.com/viewjob?jk=88370938985e0439</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Engineer, SRE TechOps CICD (Remote)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, RDS, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Kafka, Oracle, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b325f2f84b39b8</t>
+          <t>https://www.indeed.com/viewjob?jk=02946a77bdd7bddf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Colas</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Time Travel</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, SQS, SNS, RDS, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,49 +706,49 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623e6ba410872463</t>
+          <t>https://www.indeed.com/viewjob?jk=37b325f2f84b39b8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (On-Site)</t>
+          <t>Senior Data Engineer, Databricks</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Colas</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, PostgreSQL, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Photon, Spark, PySpark, Time Travel</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d460a6aac4fd260a</t>
+          <t>https://www.indeed.com/viewjob?jk=623e6ba410872463</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afe1d38414cdf113</t>
+          <t>https://www.indeed.com/viewjob?jk=d460a6aac4fd260a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,24 +801,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
+          <t>AWS, Kinesis, SQS, SNS, Scala, Kafka, Snowflake, Oracle, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=986170411aab2db0</t>
+          <t>https://www.indeed.com/viewjob?jk=afe1d38414cdf113</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Engineer II, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e33354ecb78e1f09</t>
+          <t>https://www.indeed.com/viewjob?jk=986170411aab2db0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Technical Software Engineer</t>
+          <t>Sr. Engineer II, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
+          <t>https://www.indeed.com/viewjob?jk=e33354ecb78e1f09</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack Developer [development, QA automation, data]</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,69 +906,69 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
+          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
+          <t>Full Stack Developer [development, QA automation, data]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
+          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior Engineer - Data Platforms &amp; Full Stack Applications</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
+          <t>https://www.indeed.com/viewjob?jk=8202ee33c7bd4ddb</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Identity &amp; Access Management (CIAM) Engineer</t>
+          <t>Senior Data Engineer, Global</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50d50511fbcccef</t>
+          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GCP Architect Grade C2</t>
+          <t>Senior Identity &amp; Access Management (CIAM) Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
+          <t>https://www.indeed.com/viewjob?jk=b50d50511fbcccef</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Architect Grade C2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
+          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
+          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1191,29 +1191,29 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer, Global</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Mid- Level Data Engineer, Global</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Vantage Data Centers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
+          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
         </is>
       </c>
     </row>
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer NEX</t>
+          <t>Jr Software Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Patterson-UTI Drilling Company LLC</t>
+          <t>KBR</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
+          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer NEX</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Pharmacy Data Management, Inc.</t>
+          <t>Patterson-UTI Drilling Company LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
+          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer - Digital Site Development</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>Pharmacy Data Management, Inc.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Poland, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
+          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
         </is>
       </c>
     </row>
@@ -1483,25 +1483,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QA Software Engineer NC Hybrid</t>
+          <t>Software Engineer - Digital Site Development</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
+          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
+          <t>QA Software Engineer NC Hybrid</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
+          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
+          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>True Zero Technologies</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>True Zero Technologies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Nestlé Purina</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, MLOps</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f94258f281c4987</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Agentic AI Engineering Architect (Remote -US)</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
+          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Agentic AI Engineering Architect (Remote -US)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
+          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,17 +2201,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
+          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e024f9d8e8b3e663</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Engineer, IT</t>
+          <t>Senior PowerBI Developer (FDOT OOC)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Builders FirstSource</t>
+          <t>TECKpert</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Kafka, Data Modeling, ETL, ELT, Azure DevOps</t>
+          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c466b81a1e58bbc1</t>
+          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0e614ab8a814af8</t>
+          <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43758220211affc5</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cd8a354931554ad</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer - Payrix</t>
+          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f5320968e880f71</t>
+          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Forward Deployed Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CoorsTek</t>
+          <t>Elm &amp; Oak Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Golden, CO, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ed04213140d7749</t>
+          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
+          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Law School Admission Council</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Newtown, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
+          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>New Relic</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Senior Software Engineer, Platform Infrastructure</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>SmarterDx</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,295 +2761,15 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Senior PowerBI Developer (FDOT OOC)</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>TECKpert</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Law School Admission Council</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Newtown, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Elm &amp; Oak Health</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Rochester, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>New Relic</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>DevOps Engineer II</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Level Data, Inc</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Azure DevOps, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a7875d6817c19bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Milwaukee Tool</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Menomonee Falls, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Platform Infrastructure</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>SmarterDx</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
         </is>

--- a/results/job_matches_2026-08-15.xlsx
+++ b/results/job_matches_2026-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Technical Software Engineer</t>
+          <t>Full Stack Developer [development, QA automation, data]</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
+          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Full Stack Developer [development, QA automation, data]</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
+          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Senior Site Reliability Engineer NEX</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Patterson-UTI Drilling Company LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b738036437ddf04e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Jr Software Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>KBR</t>
+          <t>Pharmacy Data Management, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Poland, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, Scala, Oracle, PostgreSQL, MySQL, MongoDB, Tableau, CI/CD, Maven</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b93c51b7c99cc5</t>
+          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer NEX</t>
+          <t>Software Engineer II - AI/ML Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Patterson-UTI Drilling Company LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
+          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pharmacy Data Management, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
+          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML Developer</t>
+          <t>QA Software Engineer NC Hybrid</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
+          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer - Digital Site Development</t>
+          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>True Zero Technologies</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, GCP, Scala, Kafka, SQL Server, NoSQL, Data Modeling</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26618760ad342643</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>QA Software Engineer NC Hybrid</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>LevelUp</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,29 +1571,29 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
+          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>True Zero Technologies</t>
+          <t>Slate Auto</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1602,11 +1602,11 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
+          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
+          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Solution Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LevelUp</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
+          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>SMTS IT Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Slate Auto</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>IT Cloud Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
+          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>Networking for Future, Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
+          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SMTS IT Engineer</t>
+          <t>Senior Software Engineer I, Research Informatics</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Mammoth Biosciences</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer II</t>
+          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Networking for Future, Inc.</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Research Informatics</t>
+          <t>Agentic AI Engineering Architect (Remote -US)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Mammoth Biosciences</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
+          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
+          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
+          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
+          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,67 +2106,67 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
+          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Agentic AI Engineering Architect (Remote -US)</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,19 +2176,19 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2197,11 +2197,11 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
+          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ROYAL ELECTRIC</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70c82340e7a51690</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Senior PowerBI Developer (FDOT OOC)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>TECKpert</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
+          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior PowerBI Developer (FDOT OOC)</t>
+          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TECKpert</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
+          <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Accenture</t>
+          <t>Elm &amp; Oak Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
+          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Milwaukee Tool</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
+          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Senior Software Engineer, Platform Infrastructure</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>SmarterDx</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
+          <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Law School Admission Council</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Newtown, PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,182 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Elm &amp; Oak Health</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Rochester, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Milwaukee Tool</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Menomonee Falls, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Law School Admission Council</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Newtown, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Associate Software Engineer - Java (Distributed Systems and Databases)</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>New Relic</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MySQL, MongoDB, DynamoDB, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4a94f26ebfc6f</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Platform Infrastructure</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>SmarterDx</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-15.xlsx
+++ b/results/job_matches_2026-08-15.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Full Stack Developer [development, QA automation, data]</t>
+          <t>Cyber Full-Stack Technical Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Delan Associates, Inc</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
+          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cyber Full-Stack Technical Software Engineer</t>
+          <t>Full Stack Developer [development, QA automation, data]</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Delan Associates, Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,17 +941,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>Azure, GCP, BigQuery, Dataflow, Snowflake, Oracle, SQL Server, ETL, Talend, Power BI</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18a8f76fdfd6054e</t>
+          <t>https://www.indeed.com/viewjob?jk=614dc194a49ca09a</t>
         </is>
       </c>
     </row>
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Global</t>
+          <t>Senior Identity &amp; Access Management (CIAM) Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, PostgreSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cfe15e3ae5e2ea78</t>
+          <t>https://www.indeed.com/viewjob?jk=b50d50511fbcccef</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Identity &amp; Access Management (CIAM) Engineer</t>
+          <t>GCP Architect Grade C2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50d50511fbcccef</t>
+          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>GCP Architect Grade C2</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala, Data Modeling</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89c367e2b7f51872</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0d5b1a5cb3ad7a</t>
+          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Blaine, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7614dc00bbe52b10</t>
+          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Blaine, MN, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1191,72 +1191,72 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=750e94d18745c7af</t>
+          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Pharmacy Data Management, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Poland, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7c81d65ca7b59b</t>
+          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Mid- Level Data Engineer, Global</t>
+          <t>Software Engineer II - AI/ML Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Vantage Data Centers</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Data Modeling, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2eceb897f127f85</t>
+          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer NEX</t>
+          <t>Software Engineer III - AI/ML Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Patterson-UTI Drilling Company LLC</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,102 +1301,102 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e23128c778b77a9</t>
+          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>QA Software Engineer NC Hybrid</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Pharmacy Data Management, Inc.</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland, OH, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, S3, ECS, RDS, Scala, SQL Server</t>
+          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f591a25dd32ad38</t>
+          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer II - AI/ML Developer</t>
+          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2968fbd1098705ab</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Developer</t>
+          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>True Zero Technologies</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccd4e6bffd7c1c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>QA Software Engineer NC Hybrid</t>
+          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=82619da05a4e5b27</t>
+          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer - Cybersecurity Analytics - Onsite</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>LevelUp</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, IAM, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bb02eacc6e0c34</t>
+          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Cloud / DevSecOps Engineer (R-00200)</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>True Zero Technologies</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe0932bbecc591b</t>
+          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Cloud Native - AI Detection and Response (AIDR) (Hybrid, Sunnyvale)</t>
+          <t>SMTS IT Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>AMD</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d5c618b9b4cf74f4</t>
+          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>IT Cloud Engineer II</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LevelUp</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brooklyn, NY, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Snowflake Schema, dbt, Power BI, Tableau, Airflow</t>
+          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce9a7a371c99d3f5</t>
+          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud Systems Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Slate Auto</t>
+          <t>Networking for Future, Inc.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, IAM, RDS, Spark, Scala, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=812be7ff2c58a8e5</t>
+          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer I, Research Informatics</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Mammoth Biosciences</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77f8f5e4e6fc8123</t>
+          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Solution Engineer</t>
+          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Experian</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, Scala, ETL</t>
+          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db39abaf672f49a6</t>
+          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SMTS IT Engineer</t>
+          <t>GCP Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>AMD</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala, Kafka</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c854612fc1752d57</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IT Cloud Engineer II</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Merrimack, NH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, Scala, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83aaaf3ac879f7b6</t>
+          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Networking for Future, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, Splunk, CI/CD, Terraform, AWS CloudFormation, Kubernetes</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22447d3211df125b</t>
+          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I, Research Informatics</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mammoth Biosciences</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Data Modeling, ETL, dbt, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbcca0bf1c89f031</t>
+          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Platform Professional Services Sr. Consultant- Cloud (Remote)</t>
+          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, GCP, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=359dab24438d038b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Agentic AI Engineering Architect (Remote -US)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>OMG Technology</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, ETL, Airflow, Apache Airflow, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ecfce2ce50a767f</t>
+          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Agentic AI Engineering Architect (Remote -US)</t>
+          <t>AI Data Scientist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>OMG Technology</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Snowflake, PostgreSQL, CI/CD, Azure DevOps, Terraform, Docker</t>
+          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,19 +1931,19 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ccaaffaf8007eb85</t>
+          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Data Scientist</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1952,11 +1952,11 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, NoSQL, Data Modeling, MLOps, CI/CD, Git, Python</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,164 +1966,164 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bafe15fb980f9aa</t>
+          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>FujiFilm</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Merrimack, NH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3da42b71924a8f2a</t>
+          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4292233ac9b01465</t>
+          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1658d63cbf8ef75d</t>
+          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. SDET Engineer (Playwright / RestAssured / FTE / Onsite)</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Redapt inc</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, CI/CD, Jenkins, Maven, Docker, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8b3f8813e95cd86</t>
+          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Senior PowerBI Developer (FDOT OOC)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>TECKpert</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79b401774b372da8</t>
+          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Snowflake &amp; AWS</t>
+          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FujiFilm</t>
+          <t>Accenture</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d1e0212686538a7</t>
+          <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise Data Hub (AWS + Snowflake + DBT + PySpark + CI/CD)</t>
+          <t>Senior QA Automation Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>VIVA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Spark, PySpark, Scala, Snowflake, Data Modeling, Star Schema, Snowflake Schema, Dimension Tables, dbt</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b95c42f66fb511bd</t>
+          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Container Platform Engineer</t>
+          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=563e90bdfc586fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior QA Automation Engineer</t>
+          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>CrowdStrike</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Tableau, CI/CD, Azure DevOps, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec78d276bddbab3e</t>
+          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Elm &amp; Oak Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3dca3bbc7e3b91c</t>
+          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SDET - AI Detection and Response (AIDR) (Hybrid)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CrowdStrike</t>
+          <t>Law School Admission Council</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Newtown, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Kafka, Oracle, PostgreSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ba38e9d47a3feabf</t>
+          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Database Engineer</t>
+          <t>Senior Software Engineer, Platform Infrastructure</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Redapt inc</t>
+          <t>SmarterDx</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,227 +2376,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f4541f6639d9bc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Senior PowerBI Developer (FDOT OOC)</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>TECKpert</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Tallahassee, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Azure, Data Factory, Dataflow, Oracle, SQL Server, Dimensional Modeling, Star Schema, Power BI</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3df96b00481cbb0c</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Senior Java Software Engineer - On-Site Minneapolis, MN</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Accenture</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Minneapolis, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, NoSQL, CI/CD, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=681a949fc99e68d5</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Elm &amp; Oak Health</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Rochester, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, SQL Server, dbt</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b95ca350f26a5100</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Sr Data Engineer</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Milwaukee Tool</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Menomonee Falls, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60bd36ef9cdb09ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Platform Infrastructure</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>SmarterDx</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Snowflake, DynamoDB, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=7e52b444a199f4fc</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Law School Admission Council</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Newtown, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Azure Cosmos DB, Power BI, CI/CD, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1b53095d8bc376d7</t>
         </is>
       </c>
     </row>
